--- a/output/pdf_financials_xlsx/BAV.H.xlsx
+++ b/output/pdf_financials_xlsx/BAV.H.xlsx
@@ -5694,49 +5694,49 @@
         <v>2.799492</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>5.8587</v>
+        <v>5.476431</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.511284</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.54716</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.570602</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.570602</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.975202</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.975202</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.975202</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.975202</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.975202</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.975202</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.975202</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.975202</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.975202</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.975202</v>
       </c>
     </row>
     <row r="93">
@@ -9342,7 +9342,11 @@
           <t>Reserves (Note 8) 6,975,202</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10312,7 +10316,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10956,7 +10964,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11500,7 +11512,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12576,7 +12592,11 @@
           <t>Reserves (Note 9) 6,975,202</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -13326,7 +13346,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -13706,7 +13730,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -15344,7 +15372,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16992,7 +17024,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>2.799492</v>
       </c>

--- a/output/pdf_financials_xlsx/BAV.H.xlsx
+++ b/output/pdf_financials_xlsx/BAV.H.xlsx
@@ -934,16 +934,16 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>1.665429</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>1.911085</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>2.235023</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>2.371487</v>
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
@@ -991,16 +991,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>-1.665429</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0</v>
+        <v>-1.911085</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0</v>
+        <v>-2.235023</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
+        <v>-2.371487</v>
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01271</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>-0.058838</v>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.482256</v>
+        <v>-0.469546</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-5.035459</v>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.482256</v>
+        <v>-0.469546</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-5.035459</v>
@@ -2353,40 +2353,40 @@
         <v>0.094364</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.013365</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.09826699999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.015954</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.001059</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.025754</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.005818</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>8.899999999999999e-05</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004962</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.00139</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.000992</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.000131</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000131</v>
       </c>
     </row>
     <row r="35">
@@ -2463,40 +2463,40 @@
         <v>0.094364</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.013365</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.09826699999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.015954</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.001059</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.025754</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.005818</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>8.899999999999999e-05</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.004962</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.00139</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.000992</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.000131</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000131</v>
       </c>
     </row>
     <row r="37">
@@ -3123,40 +3123,40 @@
         <v>0.717429</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.611173</v>
+        <v>0.597808</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.116904</v>
+        <v>0.018637</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.015954</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.001059</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.025754</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.005818</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>8.899999999999999e-05</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.004962</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.00139</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.000992</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.000131</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.000131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -30014,7 +30014,11 @@
           <t>General and administration expenses (Note 6) $</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -30284,7 +30288,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -30343,16 +30347,16 @@
         </is>
       </c>
       <c r="P233" s="5" t="n">
-        <v>-1.665429</v>
+        <v>1.665429</v>
       </c>
       <c r="Q233" s="5" t="n">
-        <v>-1.911085</v>
+        <v>1.911085</v>
       </c>
       <c r="R233" s="5" t="n">
-        <v>-2.235023</v>
+        <v>2.235023</v>
       </c>
       <c r="S233" s="5" t="n">
-        <v>-2.371487</v>
+        <v>2.371487</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -30718,7 +30722,11 @@
           <t>General and administration expenses (Note 7) $</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -31002,7 +31010,11 @@
           <t>General and administration expenses (Note 8) $</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -31284,7 +31296,11 @@
           <t>General and administration expenses $</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -32710,7 +32726,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
         <v>0.213264</v>
       </c>
@@ -34328,7 +34348,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -36162,7 +36186,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E295" s="5" t="n">
